--- a/r4-JoanneumResearch-PreNUDGE-AppData-main/StructureDefinition-at-prenudge-questionnaireresponse.xlsx
+++ b/r4-JoanneumResearch-PreNUDGE-AppData-main/StructureDefinition-at-prenudge-questionnaireresponse.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-22T11:57:51+00:00</t>
+    <t>2026-02-25T07:03:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-JoanneumResearch-PreNUDGE-AppData-main/StructureDefinition-at-prenudge-questionnaireresponse.xlsx
+++ b/r4-JoanneumResearch-PreNUDGE-AppData-main/StructureDefinition-at-prenudge-questionnaireresponse.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-25T07:03:20+00:00</t>
+    <t>2026-02-26T10:01:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -593,7 +593,7 @@
     <t>QuestionnaireResponse.identifier.system</t>
   </si>
   <si>
-    <t>The namespace for the identifier value, if no other information is given, use your website url</t>
+    <t>The namespace for the identifier value, if no other specifications are given, use your website url</t>
   </si>
   <si>
     <t>Establishes the namespace for the value - that is, a URL that describes a set values that are unique.</t>

--- a/r4-JoanneumResearch-PreNUDGE-AppData-main/StructureDefinition-at-prenudge-questionnaireresponse.xlsx
+++ b/r4-JoanneumResearch-PreNUDGE-AppData-main/StructureDefinition-at-prenudge-questionnaireresponse.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-26T10:01:13+00:00</t>
+    <t>2026-02-28T09:14:32+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-JoanneumResearch-PreNUDGE-AppData-main/StructureDefinition-at-prenudge-questionnaireresponse.xlsx
+++ b/r4-JoanneumResearch-PreNUDGE-AppData-main/StructureDefinition-at-prenudge-questionnaireresponse.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-28T09:14:32+00:00</t>
+    <t>2026-03-01T10:29:33+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-JoanneumResearch-PreNUDGE-AppData-main/StructureDefinition-at-prenudge-questionnaireresponse.xlsx
+++ b/r4-JoanneumResearch-PreNUDGE-AppData-main/StructureDefinition-at-prenudge-questionnaireresponse.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-01T10:29:33+00:00</t>
+    <t>2026-03-01T15:46:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-JoanneumResearch-PreNUDGE-AppData-main/StructureDefinition-at-prenudge-questionnaireresponse.xlsx
+++ b/r4-JoanneumResearch-PreNUDGE-AppData-main/StructureDefinition-at-prenudge-questionnaireresponse.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-01T15:46:45+00:00</t>
+    <t>2026-03-02T16:20:44+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-JoanneumResearch-PreNUDGE-AppData-main/StructureDefinition-at-prenudge-questionnaireresponse.xlsx
+++ b/r4-JoanneumResearch-PreNUDGE-AppData-main/StructureDefinition-at-prenudge-questionnaireresponse.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-02T16:20:44+00:00</t>
+    <t>2026-03-02T17:40:54+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-JoanneumResearch-PreNUDGE-AppData-main/StructureDefinition-at-prenudge-questionnaireresponse.xlsx
+++ b/r4-JoanneumResearch-PreNUDGE-AppData-main/StructureDefinition-at-prenudge-questionnaireresponse.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-02T17:40:54+00:00</t>
+    <t>2026-03-03T16:09:57+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-JoanneumResearch-PreNUDGE-AppData-main/StructureDefinition-at-prenudge-questionnaireresponse.xlsx
+++ b/r4-JoanneumResearch-PreNUDGE-AppData-main/StructureDefinition-at-prenudge-questionnaireresponse.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-03T16:09:57+00:00</t>
+    <t>2026-03-03T18:16:34+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-JoanneumResearch-PreNUDGE-AppData-main/StructureDefinition-at-prenudge-questionnaireresponse.xlsx
+++ b/r4-JoanneumResearch-PreNUDGE-AppData-main/StructureDefinition-at-prenudge-questionnaireresponse.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-03T18:16:34+00:00</t>
+    <t>2026-03-03T20:10:31+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-JoanneumResearch-PreNUDGE-AppData-main/StructureDefinition-at-prenudge-questionnaireresponse.xlsx
+++ b/r4-JoanneumResearch-PreNUDGE-AppData-main/StructureDefinition-at-prenudge-questionnaireresponse.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1523" uniqueCount="350">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1523" uniqueCount="351">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-03T20:10:31+00:00</t>
+    <t>2026-03-24T11:22:25+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -84,7 +84,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>This FHIR profile is defining the overall Questionnaire Response for PreNUDGE.</t>
+    <t>This FHIR profile is defining the overall Questionnaire Response for PreNUDGE. Be aware that if the user enters values from a device into a questionnaire, it is still considered a manual input. Please keep in mind that all questionnaire responses must comply with the qualification matrix on https://prenudge.at/qualificationmatrix/.</t>
   </si>
   <si>
     <t>Purpose</t>
@@ -756,7 +756,7 @@
     <t>QuestionnaireResponse.status</t>
   </si>
   <si>
-    <t>in-progress | completed | amended | entered-in-error | stopped</t>
+    <t>In PreNUDGE only completed QuestionnaireResponses are beeing accepted</t>
   </si>
   <si>
     <t>The position of the questionnaire response within its overall lifecycle.</t>
@@ -766,6 +766,9 @@
   </si>
   <si>
     <t>The information on Questionnaire resources  may possibly be gathered during multiple sessions and altered after considered being finished.</t>
+  </si>
+  <si>
+    <t>completed</t>
   </si>
   <si>
     <t>Lifecycle status of the questionnaire response.</t>
@@ -3961,7 +3964,7 @@
         <v>21</v>
       </c>
       <c r="S23" t="s" s="2">
-        <v>21</v>
+        <v>242</v>
       </c>
       <c r="T23" t="s" s="2">
         <v>21</v>
@@ -3979,10 +3982,10 @@
         <v>170</v>
       </c>
       <c r="Y23" t="s" s="2">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="Z23" t="s" s="2">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="AA23" t="s" s="2">
         <v>21</v>
@@ -4015,25 +4018,25 @@
         <v>100</v>
       </c>
       <c r="AK23" t="s" s="2">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="AL23" t="s" s="2">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="AM23" t="s" s="2">
-        <v>246</v>
+        <v>247</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="s" s="2">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="E24" s="2"/>
       <c r="F24" t="s" s="2">
@@ -4052,19 +4055,19 @@
         <v>89</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="N24" t="s" s="2">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="O24" t="s" s="2">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="P24" t="s" s="2">
         <v>21</v>
@@ -4113,7 +4116,7 @@
         <v>21</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>78</v>
@@ -4128,21 +4131,21 @@
         <v>100</v>
       </c>
       <c r="AK24" t="s" s="2">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="AL24" t="s" s="2">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="AM24" t="s" s="2">
-        <v>256</v>
+        <v>257</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="s" s="2">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -4165,19 +4168,19 @@
         <v>89</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="N25" t="s" s="2">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="O25" t="s" s="2">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="P25" t="s" s="2">
         <v>21</v>
@@ -4226,7 +4229,7 @@
         <v>21</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>78</v>
@@ -4241,25 +4244,25 @@
         <v>100</v>
       </c>
       <c r="AK25" t="s" s="2">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="AL25" t="s" s="2">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="AM25" t="s" s="2">
-        <v>265</v>
+        <v>266</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="s" s="2">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="E26" s="2"/>
       <c r="F26" t="s" s="2">
@@ -4278,19 +4281,19 @@
         <v>89</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="N26" t="s" s="2">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="O26" t="s" s="2">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="P26" t="s" s="2">
         <v>21</v>
@@ -4339,7 +4342,7 @@
         <v>21</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>78</v>
@@ -4354,25 +4357,25 @@
         <v>100</v>
       </c>
       <c r="AK26" t="s" s="2">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="AL26" t="s" s="2">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="AM26" t="s" s="2">
-        <v>275</v>
+        <v>276</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="s" s="2">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="E27" s="2"/>
       <c r="F27" t="s" s="2">
@@ -4391,19 +4394,19 @@
         <v>89</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="N27" t="s" s="2">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="O27" t="s" s="2">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="P27" t="s" s="2">
         <v>21</v>
@@ -4452,7 +4455,7 @@
         <v>21</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>78</v>
@@ -4467,21 +4470,21 @@
         <v>100</v>
       </c>
       <c r="AK27" t="s" s="2">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="AL27" t="s" s="2">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="AM27" t="s" s="2">
-        <v>285</v>
+        <v>286</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="s" s="2">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -4504,19 +4507,19 @@
         <v>89</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="N28" t="s" s="2">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="O28" t="s" s="2">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="P28" t="s" s="2">
         <v>21</v>
@@ -4565,7 +4568,7 @@
         <v>21</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>78</v>
@@ -4583,18 +4586,18 @@
         <v>21</v>
       </c>
       <c r="AL28" t="s" s="2">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="AM28" t="s" s="2">
-        <v>293</v>
+        <v>294</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="s" s="2">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -4617,16 +4620,16 @@
         <v>21</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="N29" t="s" s="2">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="O29" s="2"/>
       <c r="P29" t="s" s="2">
@@ -4676,7 +4679,7 @@
         <v>21</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>78</v>
@@ -4688,13 +4691,13 @@
         <v>21</v>
       </c>
       <c r="AJ29" t="s" s="2">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="AK29" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AL29" t="s" s="2">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="AM29" t="s" s="2">
         <v>21</v>
@@ -4702,10 +4705,10 @@
     </row>
     <row r="30">
       <c r="A30" t="s" s="2">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -4811,10 +4814,10 @@
     </row>
     <row r="31">
       <c r="A31" t="s" s="2">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -4922,14 +4925,14 @@
     </row>
     <row r="32">
       <c r="A32" t="s" s="2">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="E32" s="2"/>
       <c r="F32" t="s" s="2">
@@ -4951,10 +4954,10 @@
         <v>134</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="N32" t="s" s="2">
         <v>137</v>
@@ -5009,7 +5012,7 @@
         <v>21</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>78</v>
@@ -5035,10 +5038,10 @@
     </row>
     <row r="33">
       <c r="A33" t="s" s="2">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -5064,14 +5067,14 @@
         <v>154</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="N33" s="2"/>
       <c r="O33" t="s" s="2">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="P33" t="s" s="2">
         <v>21</v>
@@ -5120,7 +5123,7 @@
         <v>21</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>88</v>
@@ -5138,7 +5141,7 @@
         <v>21</v>
       </c>
       <c r="AL33" t="s" s="2">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="AM33" t="s" s="2">
         <v>21</v>
@@ -5146,10 +5149,10 @@
     </row>
     <row r="34">
       <c r="A34" t="s" s="2">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -5175,16 +5178,16 @@
         <v>102</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="N34" t="s" s="2">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="O34" t="s" s="2">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="P34" t="s" s="2">
         <v>21</v>
@@ -5233,7 +5236,7 @@
         <v>21</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>78</v>
@@ -5251,7 +5254,7 @@
         <v>21</v>
       </c>
       <c r="AL34" t="s" s="2">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="AM34" t="s" s="2">
         <v>21</v>
@@ -5259,10 +5262,10 @@
     </row>
     <row r="35">
       <c r="A35" t="s" s="2">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -5288,14 +5291,14 @@
         <v>154</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="N35" s="2"/>
       <c r="O35" t="s" s="2">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="P35" t="s" s="2">
         <v>21</v>
@@ -5344,7 +5347,7 @@
         <v>21</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>78</v>
@@ -5362,7 +5365,7 @@
         <v>21</v>
       </c>
       <c r="AL35" t="s" s="2">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="AM35" t="s" s="2">
         <v>21</v>
@@ -5370,10 +5373,10 @@
     </row>
     <row r="36">
       <c r="A36" t="s" s="2">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -5396,16 +5399,16 @@
         <v>21</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="N36" t="s" s="2">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="O36" s="2"/>
       <c r="P36" t="s" s="2">
@@ -5455,7 +5458,7 @@
         <v>21</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>78</v>
@@ -5473,7 +5476,7 @@
         <v>21</v>
       </c>
       <c r="AL36" t="s" s="2">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="AM36" t="s" s="2">
         <v>21</v>
@@ -5481,10 +5484,10 @@
     </row>
     <row r="37">
       <c r="A37" t="s" s="2">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -5590,10 +5593,10 @@
     </row>
     <row r="38">
       <c r="A38" t="s" s="2">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -5701,14 +5704,14 @@
     </row>
     <row r="39">
       <c r="A39" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="E39" s="2"/>
       <c r="F39" t="s" s="2">
@@ -5730,10 +5733,10 @@
         <v>134</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="N39" t="s" s="2">
         <v>137</v>
@@ -5788,7 +5791,7 @@
         <v>21</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>78</v>
@@ -5814,10 +5817,10 @@
     </row>
     <row r="40">
       <c r="A40" t="s" s="2">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -5840,19 +5843,19 @@
         <v>21</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="N40" t="s" s="2">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="O40" t="s" s="2">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="P40" t="s" s="2">
         <v>21</v>
@@ -5877,13 +5880,13 @@
         <v>21</v>
       </c>
       <c r="X40" t="s" s="2">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="Y40" t="s" s="2">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="Z40" t="s" s="2">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="AA40" t="s" s="2">
         <v>21</v>
@@ -5901,7 +5904,7 @@
         <v>21</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>78</v>
@@ -5919,7 +5922,7 @@
         <v>21</v>
       </c>
       <c r="AL40" t="s" s="2">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="AM40" t="s" s="2">
         <v>21</v>
@@ -5927,10 +5930,10 @@
     </row>
     <row r="41">
       <c r="A41" t="s" s="2">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -5956,14 +5959,14 @@
         <v>80</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="N41" s="2"/>
       <c r="O41" t="s" s="2">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="P41" t="s" s="2">
         <v>21</v>
@@ -6012,7 +6015,7 @@
         <v>21</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>78</v>
@@ -6030,7 +6033,7 @@
         <v>21</v>
       </c>
       <c r="AL41" t="s" s="2">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="AM41" t="s" s="2">
         <v>21</v>
@@ -6038,10 +6041,10 @@
     </row>
     <row r="42">
       <c r="A42" t="s" s="2">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -6067,14 +6070,14 @@
         <v>80</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="N42" s="2"/>
       <c r="O42" t="s" s="2">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="P42" t="s" s="2">
         <v>21</v>
@@ -6123,7 +6126,7 @@
         <v>21</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>78</v>
@@ -6141,7 +6144,7 @@
         <v>21</v>
       </c>
       <c r="AL42" t="s" s="2">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="AM42" t="s" s="2">
         <v>21</v>

--- a/r4-JoanneumResearch-PreNUDGE-AppData-main/StructureDefinition-at-prenudge-questionnaireresponse.xlsx
+++ b/r4-JoanneumResearch-PreNUDGE-AppData-main/StructureDefinition-at-prenudge-questionnaireresponse.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-24T11:22:25+00:00</t>
+    <t>2026-03-27T21:20:49+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -473,7 +473,7 @@
 </t>
   </si>
   <si>
-    <t>Unique id for this set of answers, at least one is assigned by the data provider</t>
+    <t>Mandatory date the answers were gathered</t>
   </si>
   <si>
     <t>A business identifier assigned to a particular completed (or partially completed) questionnaire.</t>
@@ -4266,7 +4266,7 @@
       </c>
       <c r="E26" s="2"/>
       <c r="F26" t="s" s="2">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="G26" t="s" s="2">
         <v>88</v>

--- a/r4-JoanneumResearch-PreNUDGE-AppData-main/StructureDefinition-at-prenudge-questionnaireresponse.xlsx
+++ b/r4-JoanneumResearch-PreNUDGE-AppData-main/StructureDefinition-at-prenudge-questionnaireresponse.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-27T21:20:49+00:00</t>
+    <t>2026-03-29T11:39:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-JoanneumResearch-PreNUDGE-AppData-main/StructureDefinition-at-prenudge-questionnaireresponse.xlsx
+++ b/r4-JoanneumResearch-PreNUDGE-AppData-main/StructureDefinition-at-prenudge-questionnaireresponse.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-29T11:39:37+00:00</t>
+    <t>2026-03-29T11:44:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-JoanneumResearch-PreNUDGE-AppData-main/StructureDefinition-at-prenudge-questionnaireresponse.xlsx
+++ b/r4-JoanneumResearch-PreNUDGE-AppData-main/StructureDefinition-at-prenudge-questionnaireresponse.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-29T11:44:39+00:00</t>
+    <t>2026-04-03T14:50:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-JoanneumResearch-PreNUDGE-AppData-main/StructureDefinition-at-prenudge-questionnaireresponse.xlsx
+++ b/r4-JoanneumResearch-PreNUDGE-AppData-main/StructureDefinition-at-prenudge-questionnaireresponse.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-03T14:50:23+00:00</t>
+    <t>2026-05-18T08:38:27+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-JoanneumResearch-PreNUDGE-AppData-main/StructureDefinition-at-prenudge-questionnaireresponse.xlsx
+++ b/r4-JoanneumResearch-PreNUDGE-AppData-main/StructureDefinition-at-prenudge-questionnaireresponse.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-18T08:38:27+00:00</t>
+    <t>2026-05-18T10:23:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-JoanneumResearch-PreNUDGE-AppData-main/StructureDefinition-at-prenudge-questionnaireresponse.xlsx
+++ b/r4-JoanneumResearch-PreNUDGE-AppData-main/StructureDefinition-at-prenudge-questionnaireresponse.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-18T10:23:40+00:00</t>
+    <t>2026-06-01T14:49:28+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-JoanneumResearch-PreNUDGE-AppData-main/StructureDefinition-at-prenudge-questionnaireresponse.xlsx
+++ b/r4-JoanneumResearch-PreNUDGE-AppData-main/StructureDefinition-at-prenudge-questionnaireresponse.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-01T14:49:28+00:00</t>
+    <t>2026-06-03T09:07:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-JoanneumResearch-PreNUDGE-AppData-main/StructureDefinition-at-prenudge-questionnaireresponse.xlsx
+++ b/r4-JoanneumResearch-PreNUDGE-AppData-main/StructureDefinition-at-prenudge-questionnaireresponse.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-03T09:07:40+00:00</t>
+    <t>2026-06-03T10:15:52+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-JoanneumResearch-PreNUDGE-AppData-main/StructureDefinition-at-prenudge-questionnaireresponse.xlsx
+++ b/r4-JoanneumResearch-PreNUDGE-AppData-main/StructureDefinition-at-prenudge-questionnaireresponse.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-03T10:15:52+00:00</t>
+    <t>2026-06-16T06:28:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-JoanneumResearch-PreNUDGE-AppData-main/StructureDefinition-at-prenudge-questionnaireresponse.xlsx
+++ b/r4-JoanneumResearch-PreNUDGE-AppData-main/StructureDefinition-at-prenudge-questionnaireresponse.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-16T06:28:21+00:00</t>
+    <t>2026-06-18T08:24:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-JoanneumResearch-PreNUDGE-AppData-main/StructureDefinition-at-prenudge-questionnaireresponse.xlsx
+++ b/r4-JoanneumResearch-PreNUDGE-AppData-main/StructureDefinition-at-prenudge-questionnaireresponse.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-18T08:24:24+00:00</t>
+    <t>2026-06-18T13:26:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-JoanneumResearch-PreNUDGE-AppData-main/StructureDefinition-at-prenudge-questionnaireresponse.xlsx
+++ b/r4-JoanneumResearch-PreNUDGE-AppData-main/StructureDefinition-at-prenudge-questionnaireresponse.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-18T13:26:12+00:00</t>
+    <t>2026-06-22T11:44:44+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-JoanneumResearch-PreNUDGE-AppData-main/StructureDefinition-at-prenudge-questionnaireresponse.xlsx
+++ b/r4-JoanneumResearch-PreNUDGE-AppData-main/StructureDefinition-at-prenudge-questionnaireresponse.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-22T11:44:44+00:00</t>
+    <t>2026-06-22T12:35:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-JoanneumResearch-PreNUDGE-AppData-main/StructureDefinition-at-prenudge-questionnaireresponse.xlsx
+++ b/r4-JoanneumResearch-PreNUDGE-AppData-main/StructureDefinition-at-prenudge-questionnaireresponse.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-22T12:35:22+00:00</t>
+    <t>2026-06-22T13:57:07+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-JoanneumResearch-PreNUDGE-AppData-main/StructureDefinition-at-prenudge-questionnaireresponse.xlsx
+++ b/r4-JoanneumResearch-PreNUDGE-AppData-main/StructureDefinition-at-prenudge-questionnaireresponse.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-22T13:57:07+00:00</t>
+    <t>2026-06-22T14:44:05+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-JoanneumResearch-PreNUDGE-AppData-main/StructureDefinition-at-prenudge-questionnaireresponse.xlsx
+++ b/r4-JoanneumResearch-PreNUDGE-AppData-main/StructureDefinition-at-prenudge-questionnaireresponse.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-22T14:44:05+00:00</t>
+    <t>2026-06-24T07:32:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-JoanneumResearch-PreNUDGE-AppData-main/StructureDefinition-at-prenudge-questionnaireresponse.xlsx
+++ b/r4-JoanneumResearch-PreNUDGE-AppData-main/StructureDefinition-at-prenudge-questionnaireresponse.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-24T07:32:55+00:00</t>
+    <t>2026-06-24T12:07:10+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-JoanneumResearch-PreNUDGE-AppData-main/StructureDefinition-at-prenudge-questionnaireresponse.xlsx
+++ b/r4-JoanneumResearch-PreNUDGE-AppData-main/StructureDefinition-at-prenudge-questionnaireresponse.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-24T12:07:10+00:00</t>
+    <t>2026-06-24T13:18:54+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-JoanneumResearch-PreNUDGE-AppData-main/StructureDefinition-at-prenudge-questionnaireresponse.xlsx
+++ b/r4-JoanneumResearch-PreNUDGE-AppData-main/StructureDefinition-at-prenudge-questionnaireresponse.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-24T13:18:54+00:00</t>
+    <t>2026-06-29T10:23:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-JoanneumResearch-PreNUDGE-AppData-main/StructureDefinition-at-prenudge-questionnaireresponse.xlsx
+++ b/r4-JoanneumResearch-PreNUDGE-AppData-main/StructureDefinition-at-prenudge-questionnaireresponse.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-29T10:23:22+00:00</t>
+    <t>2026-06-29T10:47:49+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-JoanneumResearch-PreNUDGE-AppData-main/StructureDefinition-at-prenudge-questionnaireresponse.xlsx
+++ b/r4-JoanneumResearch-PreNUDGE-AppData-main/StructureDefinition-at-prenudge-questionnaireresponse.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-29T10:47:49+00:00</t>
+    <t>2026-06-29T16:58:51+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-JoanneumResearch-PreNUDGE-AppData-main/StructureDefinition-at-prenudge-questionnaireresponse.xlsx
+++ b/r4-JoanneumResearch-PreNUDGE-AppData-main/StructureDefinition-at-prenudge-questionnaireresponse.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-29T16:58:51+00:00</t>
+    <t>2026-06-29T17:35:07+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-JoanneumResearch-PreNUDGE-AppData-main/StructureDefinition-at-prenudge-questionnaireresponse.xlsx
+++ b/r4-JoanneumResearch-PreNUDGE-AppData-main/StructureDefinition-at-prenudge-questionnaireresponse.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-29T17:35:07+00:00</t>
+    <t>2026-06-30T08:18:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-JoanneumResearch-PreNUDGE-AppData-main/StructureDefinition-at-prenudge-questionnaireresponse.xlsx
+++ b/r4-JoanneumResearch-PreNUDGE-AppData-main/StructureDefinition-at-prenudge-questionnaireresponse.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-30T08:18:50+00:00</t>
+    <t>2026-06-30T14:49:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-JoanneumResearch-PreNUDGE-AppData-main/StructureDefinition-at-prenudge-questionnaireresponse.xlsx
+++ b/r4-JoanneumResearch-PreNUDGE-AppData-main/StructureDefinition-at-prenudge-questionnaireresponse.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-30T14:49:39+00:00</t>
+    <t>2026-07-01T08:47:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-JoanneumResearch-PreNUDGE-AppData-main/StructureDefinition-at-prenudge-questionnaireresponse.xlsx
+++ b/r4-JoanneumResearch-PreNUDGE-AppData-main/StructureDefinition-at-prenudge-questionnaireresponse.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-01T08:47:20+00:00</t>
+    <t>2026-07-01T10:20:10+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-JoanneumResearch-PreNUDGE-AppData-main/StructureDefinition-at-prenudge-questionnaireresponse.xlsx
+++ b/r4-JoanneumResearch-PreNUDGE-AppData-main/StructureDefinition-at-prenudge-questionnaireresponse.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-01T10:20:10+00:00</t>
+    <t>2026-07-22T09:38:36+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-JoanneumResearch-PreNUDGE-AppData-main/StructureDefinition-at-prenudge-questionnaireresponse.xlsx
+++ b/r4-JoanneumResearch-PreNUDGE-AppData-main/StructureDefinition-at-prenudge-questionnaireresponse.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-22T09:38:36+00:00</t>
+    <t>2026-07-22T10:33:49+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-JoanneumResearch-PreNUDGE-AppData-main/StructureDefinition-at-prenudge-questionnaireresponse.xlsx
+++ b/r4-JoanneumResearch-PreNUDGE-AppData-main/StructureDefinition-at-prenudge-questionnaireresponse.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-22T10:33:49+00:00</t>
+    <t>2026-07-22T11:37:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-JoanneumResearch-PreNUDGE-AppData-main/StructureDefinition-at-prenudge-questionnaireresponse.xlsx
+++ b/r4-JoanneumResearch-PreNUDGE-AppData-main/StructureDefinition-at-prenudge-questionnaireresponse.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-22T11:37:23+00:00</t>
+    <t>2026-07-23T14:49:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-JoanneumResearch-PreNUDGE-AppData-main/StructureDefinition-at-prenudge-questionnaireresponse.xlsx
+++ b/r4-JoanneumResearch-PreNUDGE-AppData-main/StructureDefinition-at-prenudge-questionnaireresponse.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-23T14:49:55+00:00</t>
+    <t>2026-08-05T12:17:57+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-JoanneumResearch-PreNUDGE-AppData-main/StructureDefinition-at-prenudge-questionnaireresponse.xlsx
+++ b/r4-JoanneumResearch-PreNUDGE-AppData-main/StructureDefinition-at-prenudge-questionnaireresponse.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-05T12:17:57+00:00</t>
+    <t>2026-08-05T12:30:06+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-JoanneumResearch-PreNUDGE-AppData-main/StructureDefinition-at-prenudge-questionnaireresponse.xlsx
+++ b/r4-JoanneumResearch-PreNUDGE-AppData-main/StructureDefinition-at-prenudge-questionnaireresponse.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-05T12:30:06+00:00</t>
+    <t>2026-08-06T10:54:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-JoanneumResearch-PreNUDGE-AppData-main/StructureDefinition-at-prenudge-questionnaireresponse.xlsx
+++ b/r4-JoanneumResearch-PreNUDGE-AppData-main/StructureDefinition-at-prenudge-questionnaireresponse.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-06T10:54:53+00:00</t>
+    <t>2026-08-07T08:52:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-JoanneumResearch-PreNUDGE-AppData-main/StructureDefinition-at-prenudge-questionnaireresponse.xlsx
+++ b/r4-JoanneumResearch-PreNUDGE-AppData-main/StructureDefinition-at-prenudge-questionnaireresponse.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-07T08:52:23+00:00</t>
+    <t>2026-08-13T06:23:48+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-JoanneumResearch-PreNUDGE-AppData-main/StructureDefinition-at-prenudge-questionnaireresponse.xlsx
+++ b/r4-JoanneumResearch-PreNUDGE-AppData-main/StructureDefinition-at-prenudge-questionnaireresponse.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-13T06:23:48+00:00</t>
+    <t>2026-08-18T12:08:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-JoanneumResearch-PreNUDGE-AppData-main/StructureDefinition-at-prenudge-questionnaireresponse.xlsx
+++ b/r4-JoanneumResearch-PreNUDGE-AppData-main/StructureDefinition-at-prenudge-questionnaireresponse.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-18T12:08:37+00:00</t>
+    <t>2026-08-18T12:35:51+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-JoanneumResearch-PreNUDGE-AppData-main/StructureDefinition-at-prenudge-questionnaireresponse.xlsx
+++ b/r4-JoanneumResearch-PreNUDGE-AppData-main/StructureDefinition-at-prenudge-questionnaireresponse.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-18T12:35:51+00:00</t>
+    <t>2026-08-20T08:19:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-JoanneumResearch-PreNUDGE-AppData-main/StructureDefinition-at-prenudge-questionnaireresponse.xlsx
+++ b/r4-JoanneumResearch-PreNUDGE-AppData-main/StructureDefinition-at-prenudge-questionnaireresponse.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-20T08:19:53+00:00</t>
+    <t>2026-08-20T13:42:02+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-JoanneumResearch-PreNUDGE-AppData-main/StructureDefinition-at-prenudge-questionnaireresponse.xlsx
+++ b/r4-JoanneumResearch-PreNUDGE-AppData-main/StructureDefinition-at-prenudge-questionnaireresponse.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-20T13:42:02+00:00</t>
+    <t>2026-08-26T07:06:07+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-JoanneumResearch-PreNUDGE-AppData-main/StructureDefinition-at-prenudge-questionnaireresponse.xlsx
+++ b/r4-JoanneumResearch-PreNUDGE-AppData-main/StructureDefinition-at-prenudge-questionnaireresponse.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-26T07:06:07+00:00</t>
+    <t>2026-08-26T07:22:28+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-JoanneumResearch-PreNUDGE-AppData-main/StructureDefinition-at-prenudge-questionnaireresponse.xlsx
+++ b/r4-JoanneumResearch-PreNUDGE-AppData-main/StructureDefinition-at-prenudge-questionnaireresponse.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-26T07:22:28+00:00</t>
+    <t>2026-08-26T07:28:06+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
